--- a/appium_tests/test_cases.xlsx
+++ b/appium_tests/test_cases.xlsx
@@ -612,7 +612,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-11 13:25:13 | Target: Android App + PHP Backend API E2E Suite</t>
+          <t>Generated: 2026-06-18 08:55:05 | Target: Android App + PHP Backend API E2E Suite</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
